--- a/Pruebas calificadas/COLEGIO-CIUDADELA-EL-RECREO-SONIA-OSORIO-DE-SAINT-MALO-(IED)-1102_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO-CIUDADELA-EL-RECREO-SONIA-OSORIO-DE-SAINT-MALO-(IED)-1102_CALIFICADO.xlsx
@@ -807,11 +807,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -1060,11 +1056,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -1309,11 +1301,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -1518,11 +1506,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -1691,11 +1675,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -1864,11 +1844,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -2089,11 +2065,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -2342,11 +2314,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -2595,11 +2563,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -2848,11 +2812,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -3101,11 +3061,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -3354,11 +3310,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -3607,11 +3559,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -3860,11 +3808,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -4113,11 +4057,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -4366,11 +4306,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -4619,11 +4555,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -4872,11 +4804,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -5125,11 +5053,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -5378,11 +5302,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -5631,11 +5551,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -5884,11 +5800,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -6137,11 +6049,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -6390,11 +6298,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -6643,11 +6547,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -6896,11 +6796,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -7149,11 +7045,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -7402,11 +7294,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -7655,11 +7543,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -7908,11 +7792,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -8161,11 +8041,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -8394,11 +8270,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -8623,11 +8495,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -8876,11 +8744,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -9129,11 +8993,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -9382,11 +9242,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -9603,11 +9459,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -9856,11 +9708,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -10109,11 +9957,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -10362,11 +10206,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -10615,11 +10455,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -10868,11 +10704,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -11121,11 +10953,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -11374,11 +11202,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -11627,11 +11451,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -11880,11 +11700,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -12133,11 +11949,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -12386,11 +12198,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -12639,11 +12447,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -12888,11 +12692,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -13141,11 +12941,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -13394,11 +13190,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -13647,11 +13439,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -13900,11 +13688,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -14153,11 +13937,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -14406,11 +14186,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -14659,11 +14435,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -14912,11 +14684,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="inlineStr"/>
       <c r="B59" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -15165,11 +14933,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="inlineStr"/>
       <c r="B60" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -15418,11 +15182,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A61" s="2" t="inlineStr"/>
       <c r="B61" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
